--- a/estm/Es.xlsx
+++ b/estm/Es.xlsx
@@ -8,14 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_git\trabalho\estm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A044BA44-3C80-41E7-AB81-475EAA8A9AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF370454-4CBD-4C67-9933-902810B67744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1155" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{18667A4F-09A4-404A-8AF9-CC6CB5834135}"/>
+    <workbookView xWindow="-28920" yWindow="-1155" windowWidth="29040" windowHeight="15840" xr2:uid="{18667A4F-09A4-404A-8AF9-CC6CB5834135}"/>
   </bookViews>
   <sheets>
     <sheet name="Geral" sheetId="1" r:id="rId1"/>
     <sheet name="ESTM1" sheetId="2" r:id="rId2"/>
+    <sheet name="ESTM2" sheetId="3" r:id="rId3"/>
+    <sheet name="ESTM3" sheetId="4" r:id="rId4"/>
+    <sheet name="ESTM4" sheetId="5" r:id="rId5"/>
+    <sheet name="ESTM5" sheetId="6" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Geral!$A$1:$C$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -37,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="118">
   <si>
     <t>Release de Bandeiras</t>
   </si>
@@ -72,9 +79,6 @@
     <t>Direciona Tech</t>
   </si>
   <si>
-    <t>Datadog?</t>
-  </si>
-  <si>
     <t>Modernização Conciliação - Serviço Conciliação Contábil De Cartão Débito</t>
   </si>
   <si>
@@ -99,9 +103,6 @@
     <t>Projeto multiconexão</t>
   </si>
   <si>
-    <t>Contábil</t>
-  </si>
-  <si>
     <t>Levar dados para Mesh</t>
   </si>
   <si>
@@ -118,10 +119,6 @@
   </si>
   <si>
     <t>Observação</t>
-  </si>
-  <si>
-    <t>Vai depender do andamento da sprint 4
-A principio vou estimar 1 sprint</t>
   </si>
   <si>
     <t xml:space="preserve">DMC </t>
@@ -179,17 +176,261 @@
     <t>O desenvolvimento será iniciado na sprint 4. Estou reservando 40 horas, prevendo  transbordo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Tratar </t>
-  </si>
-  <si>
     <t>Normalmente é estimado um valor fixo. Verificar com Marcinha qual a quantidade de horas que normalmente é estimada.</t>
+  </si>
+  <si>
+    <t>Desenho de solução</t>
+  </si>
+  <si>
+    <t>Vai depender do andamento da sprint 4
+A principio estou estimando 1 sprint</t>
+  </si>
+  <si>
+    <t>Tratamento de registros base 2 sem base 1</t>
+  </si>
+  <si>
+    <t>Aumentar Resiliência do Conciliação Débito</t>
+  </si>
+  <si>
+    <t>Migrar Conciliação do arquivo T464 para Conciliação Débito</t>
+  </si>
+  <si>
+    <t>Tratar decurso de prazo de transações a partir da tabela de transações</t>
+  </si>
+  <si>
+    <t>Gap atual da Conciliação de transações, gerando falta de visão e possível diferença contábil</t>
+  </si>
+  <si>
+    <t>Pré requisito para migrar Conciliação do arquivo T464</t>
+  </si>
+  <si>
+    <t>Necessário para Desativação do antigo Conciliação, gerando redução de custo</t>
+  </si>
+  <si>
+    <t>Migrar ACL Autenticação no Segurança</t>
+  </si>
+  <si>
+    <t>Unificação dos autorizadores - Lavantamento dos impactos</t>
+  </si>
+  <si>
+    <t>Documentação</t>
+  </si>
+  <si>
+    <t>ver com Mateus</t>
+  </si>
+  <si>
+    <t>Criação da conta aws</t>
+  </si>
+  <si>
+    <t>Tratar TC 05 após tratamento de decurso de prazo</t>
+  </si>
+  <si>
+    <t>Gap da plataforma modernizada</t>
+  </si>
+  <si>
+    <t>Ver com Thiago</t>
+  </si>
+  <si>
+    <t>Ver com Nishi</t>
+  </si>
+  <si>
+    <t>Migrar ACL Autenticação no Segurança (ESTM2)</t>
+  </si>
+  <si>
+    <t>Mapeamento dos impactos (eventos x consumidores, etc), definição da solução e Refinamento</t>
+  </si>
+  <si>
+    <t>Desativar micro-serviço Fraudes Bandeiras (ESTM3)</t>
+  </si>
+  <si>
+    <t>Pré requisito Camada Zero / Simplificação e Evolução da plataforma</t>
+  </si>
+  <si>
+    <t>Adaptar Autorizador Digital para usar o Segurança para validar autenticação 3DS</t>
+  </si>
+  <si>
+    <t>Incluir função para validação de autenticação 3DS</t>
+  </si>
+  <si>
+    <t>Alterar transação CR1 para se integrar com a  transação 3DS para função de autenticação 3DS</t>
+  </si>
+  <si>
+    <t>Alterar transação 3DS para se integrar com a  transação CR1 para função de autenticação 3DS</t>
+  </si>
+  <si>
+    <t>aws - Autorizador Digital</t>
+  </si>
+  <si>
+    <t>aws - ACL Segurança</t>
+  </si>
+  <si>
+    <t>Mainframe - CR1</t>
+  </si>
+  <si>
+    <t>Mainframe - 3DS</t>
+  </si>
+  <si>
+    <t>Levantar campos que existem no contrato atual com Fraudes e não existe no transação finalizada</t>
+  </si>
+  <si>
+    <t>Alterar Formatador para direcionar transação de advice Mastercard para o Autorizador Presente</t>
+  </si>
+  <si>
+    <t>aws - Formatador</t>
+  </si>
+  <si>
+    <t>Validação e Testes do Autorizador Presente</t>
+  </si>
+  <si>
+    <t>Desativar micro-serviço Fraudes Bandeiras - Gravar transações advice mastercard no mesh</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pré requisito Camada Zero / Simplificação e Evolução da plataforma
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Necessário puxar discovery com time AQ5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Sinergia com a frente Dados </t>
+    </r>
+  </si>
+  <si>
+    <t>Alterar Formatador para direcionar todas as transações para o Autorizador</t>
+  </si>
+  <si>
+    <t>Criar produto(s) para tratar as transações direcionadas pelo Formatador</t>
+  </si>
+  <si>
+    <t>aws - Autorizador Presente</t>
+  </si>
+  <si>
+    <t>Ver com Regi</t>
+  </si>
+  <si>
+    <t>Necessário aguardar direcionamento do Cores</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>Datadog ?</t>
+  </si>
+  <si>
+    <t>Necssário alinhar com o time da Operação / Backoffice que o Chargeback será processado em D+1</t>
+  </si>
+  <si>
+    <t>Pavimentação</t>
+  </si>
+  <si>
+    <t>Implementar Cenário 1 - Erro gerado COM ocorrência X0</t>
+  </si>
+  <si>
+    <t>Implementar Cenário 2 - Erro gerado SEM ocorrência X0 - Retorno Segurança</t>
+  </si>
+  <si>
+    <t>mplementar Cenário 2 - Erro gerado SEM ocorrência X0 - Retorno Demais Serviços</t>
+  </si>
+  <si>
+    <t>Implementar Cenário 3 - Erro gerado no próprio Autorizador</t>
+  </si>
+  <si>
+    <t>Implementar Cenário 3 - Erro gerado no Conciliação</t>
+  </si>
+  <si>
+    <t>Motivo de erro Interno (ESTM5)</t>
+  </si>
+  <si>
+    <t>Incluir campo no evento Transação Finalizada e Conciliação Finalizada</t>
+  </si>
+  <si>
+    <t>Alterar Glue Job </t>
+  </si>
+  <si>
+    <t>Incluir Campo na Tabela de Transações</t>
+  </si>
+  <si>
+    <t>Incluir campo no response da API</t>
+  </si>
+  <si>
+    <t>Incluir campo nas tabelas Data Mesh</t>
+  </si>
+  <si>
+    <t>Mapeamento do campo no Autorizadores</t>
+  </si>
+  <si>
+    <t>Realizar mapeamento / engenharia reversa das ocorrências X0 retornadas pelos serviços Contas, Limite operacional e Limite Portador</t>
+  </si>
+  <si>
+    <t>Correlacionar as ocorrências X0  com os códigos de motivo do Autorizador de Crédito</t>
+  </si>
+  <si>
+    <t>Desenvolver De Para: Ocorrência X0 x Motivo Interno mapeando para o novo campo de motivo de erro interno</t>
+  </si>
+  <si>
+    <t>Autorizador</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Mapeamento dos erros retornados pelo Segurança</t>
+  </si>
+  <si>
+    <t>Criar interpretador do retorno do serviço de Segurança para montar o código de erro Interno para o novo campo de motivo de erro interno</t>
+  </si>
+  <si>
+    <t>Implementar Cenário 2 - Erro gerado SEM ocorrência X0 - BC, AQ5, CC</t>
+  </si>
+  <si>
+    <t>Criar interpretador do retorno dos serviços das siglas BC, AQ5 e CC para montar o código de erro Interno para o novo campo de motivo de erro interno</t>
+  </si>
+  <si>
+    <t>Implementar Cenário 2 - Erro gerado SEM ocorrência X0 - Demais Serviços</t>
+  </si>
+  <si>
+    <t>Criar interpretador do retorno dos demais serviços para montar o código de erro Interno para o novo campo de motivo de erro interno</t>
+  </si>
+  <si>
+    <t>Mapeamento dos erros retornados pelos serviços das siglas BC, AQ5 e CC</t>
+  </si>
+  <si>
+    <t>Mapeamento dos erros retornados pelos demais serviços</t>
+  </si>
+  <si>
+    <t>Mapeamento dos erros gerado pelo Autorizador</t>
+  </si>
+  <si>
+    <t>Ajustar Error Handler para tratar o novo campo código motivo erro interno</t>
+  </si>
+  <si>
+    <t>Implementar Cenário 4 - Erro gerado no Conciliação</t>
+  </si>
+  <si>
+    <t>Mapeamento dos erros gerado pelo Conciliação</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,8 +461,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -234,8 +487,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -258,11 +517,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -291,9 +587,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -304,9 +597,62 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -322,6 +668,290 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>7606</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20FDA39D-188C-943A-C95D-B177F6FE7CD1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7867650" y="400050"/>
+          <a:ext cx="5419725" cy="12180556"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>103290</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>151521</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4394429-D520-109B-AA58-93504C655715}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8429625" y="552450"/>
+          <a:ext cx="11876190" cy="7028571"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>446933</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>142000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{004008F7-21C8-E416-E8AF-C981E06E0E2B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9839325" y="381000"/>
+          <a:ext cx="5933333" cy="7000000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>542171</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>56262</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagem 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{973D281A-0DBA-DFA6-EC8A-B3D0D70F20E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9839325" y="8001000"/>
+          <a:ext cx="6028571" cy="7104762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>66133</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>122928</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Imagem 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8BC7F6E8-7DED-58C8-77B7-60BA79E22790}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9839325" y="15430500"/>
+          <a:ext cx="4333333" cy="7171428"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>427548</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>132465</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Imagem 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8E09791-03A0-0C0C-9D4C-3B185B6E60B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8582025" y="485775"/>
+          <a:ext cx="8619048" cy="7076190"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -641,33 +1271,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59EE2FA8-ADDF-4863-A88B-6C1D393DF8DA}">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.5703125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="10" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="73.7109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="56.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="73.28515625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5">
-        <f>SUM(B3:B4)</f>
-        <v>620</v>
-      </c>
+      <c r="B2" s="5"/>
     </row>
     <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -677,7 +1304,7 @@
         <v>500</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -688,21 +1315,18 @@
         <v>120</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="5">
-        <f>SUM(B7:B8)</f>
-        <v>696</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B6" s="5"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
-        <v>29</v>
+      <c r="A7" s="13" t="s">
+        <v>26</v>
       </c>
       <c r="B7" s="6">
         <f>ESTM1!C9</f>
@@ -710,34 +1334,31 @@
       </c>
     </row>
     <row r="8" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>22</v>
+      <c r="A8" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="B8" s="6">
         <v>360</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="5">
-        <f>B11</f>
-        <v>40</v>
-      </c>
+      <c r="B10" s="5"/>
     </row>
     <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="13" t="s">
         <v>4</v>
       </c>
       <c r="B11" s="6">
         <v>40</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -745,118 +1366,351 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B13" s="5"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
+    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="5"/>
+      <c r="B14" s="18">
+        <v>80</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
+      <c r="A15" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="6">
+        <v>120</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="A16" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="6">
+        <v>80</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="6">
+        <v>160</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="13"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="5"/>
+    </row>
+    <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="18">
+        <v>120</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" s="6">
+        <f>ESTM2!C8</f>
+        <v>344</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="6">
+        <f>ESTM3!C6</f>
+        <v>120</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="4"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="5"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" s="6">
+        <f>ESTM4!C5</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" s="5"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" s="6">
+        <v>80</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="5"/>
+    </row>
+    <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="6">
+        <v>120</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B38" s="5"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42" s="5"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" s="6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B44" s="6">
+        <v>120</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" s="5"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="5"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" s="5"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="5"/>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B28" s="5"/>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="5"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" s="5"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="B50" s="6">
+        <f>ESTM5!C3</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="B51" s="6">
+        <f>ESTM5!C11</f>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B52" s="6">
+        <f>ESTM5!C16</f>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A53" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="B53" s="6">
+        <f>ESTM5!C21</f>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A54" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="B54" s="6">
+        <f>ESTM5!C26</f>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="B55" s="6">
+        <f>ESTM5!C31</f>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="B56" s="6">
+        <f>ESTM5!C36</f>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B57" s="6">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B37" s="5"/>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B43" s="5"/>
+      <c r="B59" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C59" s="19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B62" s="5">
+        <f>SUM(B2:B61)</f>
+        <v>3932</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C1" xr:uid="{59EE2FA8-ADDF-4863-A88B-6C1D393DF8DA}"/>
   <hyperlinks>
     <hyperlink ref="A7" location="ESTM1!A1" display="Chargeback (ESTM1)" xr:uid="{A18D599B-3969-435D-86EC-B5E3E10DB233}"/>
+    <hyperlink ref="A21" location="ESTM2!A1" display="Migrar ACL Autenticação no Segurança (ESTM2)" xr:uid="{25C6114A-AFAE-4F85-BD16-E47B9D324FDB}"/>
+    <hyperlink ref="A22" location="ESTM3!A1" display="Desativar micro-serviço Fraudes Bandeiras (ESTM3)" xr:uid="{31331AC1-B46F-4D5F-A6A8-A0BDFCFD76C5}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -864,7 +1718,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDEE5CAD-01B4-41DD-928A-F6C7928763CB}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="55.140625" customWidth="1"/>
@@ -872,97 +1726,804 @@
     <col min="3" max="3" width="11.28515625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="17"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="B3" s="11"/>
+      <c r="C3" s="12">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B5" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="12">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="13">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="12" t="s">
+      <c r="C7" s="12">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="13">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="13">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="13">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="13">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="13">
+      <c r="C8" s="12">
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C9" s="9">
         <f>SUM(C3:C8)</f>
         <v>336</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="G2:O2"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F836D3-5F45-41F6-86AB-EE92AD26971D}">
+  <dimension ref="A1:O8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="85.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="17"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="12">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="12">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="12">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="12">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C8" s="9">
+        <f>SUM(C3:C7)</f>
+        <v>344</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="G2:O2"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3F7B3C2-0695-44A6-9001-E4F94DA203D5}">
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="89.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="17"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="12">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="12">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C6" s="9">
+        <f>SUM(C3:C5)</f>
+        <v>120</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="G2:O2"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7BDECCF-F7A4-43CE-A6C4-80776E3E5565}">
+  <dimension ref="A1:O5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="69" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="17"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="12">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="12">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C5" s="9">
+        <f>SUM(C3:C4)</f>
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="G2:O2"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB9A90AB-EBB2-4453-82CC-18A2F6913633}">
+  <dimension ref="A1:O39"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="70.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="23"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="25"/>
+      <c r="E2" s="23"/>
+      <c r="G2" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="17"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="28">
+        <f>SUM(C4:C9)</f>
+        <v>120</v>
+      </c>
+      <c r="D3" s="25"/>
+      <c r="E3" s="23"/>
+    </row>
+    <row r="4" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30">
+        <v>16</v>
+      </c>
+      <c r="D4" s="25"/>
+      <c r="E4" s="23"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30">
+        <v>24</v>
+      </c>
+      <c r="D5" s="25"/>
+      <c r="E5" s="23"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30">
+        <v>8</v>
+      </c>
+      <c r="D6" s="25"/>
+      <c r="E6" s="23"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30">
+        <v>24</v>
+      </c>
+      <c r="D7" s="25"/>
+      <c r="E7" s="23"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30">
+        <v>24</v>
+      </c>
+      <c r="D8" s="25"/>
+      <c r="E8" s="23"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30">
+        <v>24</v>
+      </c>
+      <c r="D9" s="25"/>
+      <c r="E9" s="23"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="25"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="23"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="31"/>
+      <c r="C11" s="28">
+        <f>SUM(C12:C14)</f>
+        <v>166</v>
+      </c>
+      <c r="D11" s="25"/>
+      <c r="E11" s="23"/>
+    </row>
+    <row r="12" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="31">
+        <v>60</v>
+      </c>
+      <c r="D12" s="25"/>
+      <c r="E12" s="23"/>
+    </row>
+    <row r="13" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="31">
+        <v>90</v>
+      </c>
+      <c r="D13" s="25"/>
+      <c r="E13" s="23"/>
+    </row>
+    <row r="14" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="31">
+        <v>16</v>
+      </c>
+      <c r="D14" s="25"/>
+      <c r="E14" s="23"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="25"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="23"/>
+    </row>
+    <row r="16" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" s="31"/>
+      <c r="C16" s="28">
+        <f>SUM(C17:C19)</f>
+        <v>122</v>
+      </c>
+      <c r="D16" s="25"/>
+      <c r="E16" s="23"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" s="31">
+        <v>16</v>
+      </c>
+      <c r="D17" s="25"/>
+      <c r="E17" s="23"/>
+    </row>
+    <row r="18" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="31">
+        <v>90</v>
+      </c>
+      <c r="D18" s="25"/>
+      <c r="E18" s="23"/>
+    </row>
+    <row r="19" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="31">
+        <v>16</v>
+      </c>
+      <c r="D19" s="25"/>
+      <c r="E19" s="23"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="25"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="23"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="5">
+        <f>SUM(C22:C24)</f>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="B22" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" s="31">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C23" s="31">
+        <v>80</v>
+      </c>
+      <c r="F23" s="33"/>
+    </row>
+    <row r="24" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C24" s="31">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" s="5">
+        <f>SUM(C27:C29)</f>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="B27" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" s="31">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="B28" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C28" s="31">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" s="31">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31" s="5">
+        <f>SUM(C32:C34)</f>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="B32" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C32" s="31">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C33" s="31">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A34" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34" s="31">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C36" s="5">
+        <f>SUM(C37:C39)</f>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="B37" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C37" s="31">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B38" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C38" s="31">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A39" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C39" s="31">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="G2:O2"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/estm/Es.xlsx
+++ b/estm/Es.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_git\trabalho\estm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF370454-4CBD-4C67-9933-902810B67744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30EA466A-8AA0-4AF4-9B80-F41B0142753B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1155" windowWidth="29040" windowHeight="15840" xr2:uid="{18667A4F-09A4-404A-8AF9-CC6CB5834135}"/>
   </bookViews>
@@ -19,9 +19,10 @@
     <sheet name="ESTM3" sheetId="4" r:id="rId4"/>
     <sheet name="ESTM4" sheetId="5" r:id="rId5"/>
     <sheet name="ESTM5" sheetId="6" r:id="rId6"/>
+    <sheet name="ESTM6" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Geral!$A$1:$C$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Geral!$A$1:$C$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="131">
   <si>
     <t>Release de Bandeiras</t>
   </si>
@@ -91,21 +92,12 @@
     <t>Camada Zero</t>
   </si>
   <si>
-    <t>Conexão direta com a Master</t>
-  </si>
-  <si>
     <t>Falcon</t>
   </si>
   <si>
     <t>Modernização Visa</t>
   </si>
   <si>
-    <t>Projeto multiconexão</t>
-  </si>
-  <si>
-    <t>Levar dados para Mesh</t>
-  </si>
-  <si>
     <t>Pré-Autorização</t>
   </si>
   <si>
@@ -169,14 +161,7 @@
     <t>Conciliação Débito</t>
   </si>
   <si>
-    <t>Precisa de uma Oportunidade / Refinamento para definir a solução para que seja possível levantar o esforço.
-A principio estou estimando 3 sprints, sendo 1 para definir solução + refinamento e 2 para iniciar desenvolvimento</t>
-  </si>
-  <si>
     <t>O desenvolvimento será iniciado na sprint 4. Estou reservando 40 horas, prevendo  transbordo.</t>
-  </si>
-  <si>
-    <t>Normalmente é estimado um valor fixo. Verificar com Marcinha qual a quantidade de horas que normalmente é estimada.</t>
   </si>
   <si>
     <t>Desenho de solução</t>
@@ -237,15 +222,9 @@
     <t>Migrar ACL Autenticação no Segurança (ESTM2)</t>
   </si>
   <si>
-    <t>Mapeamento dos impactos (eventos x consumidores, etc), definição da solução e Refinamento</t>
-  </si>
-  <si>
     <t>Desativar micro-serviço Fraudes Bandeiras (ESTM3)</t>
   </si>
   <si>
-    <t>Pré requisito Camada Zero / Simplificação e Evolução da plataforma</t>
-  </si>
-  <si>
     <t>Adaptar Autorizador Digital para usar o Segurança para validar autenticação 3DS</t>
   </si>
   <si>
@@ -258,12 +237,6 @@
     <t>Alterar transação 3DS para se integrar com a  transação CR1 para função de autenticação 3DS</t>
   </si>
   <si>
-    <t>aws - Autorizador Digital</t>
-  </si>
-  <si>
-    <t>aws - ACL Segurança</t>
-  </si>
-  <si>
     <t>Mainframe - CR1</t>
   </si>
   <si>
@@ -276,17 +249,159 @@
     <t>Alterar Formatador para direcionar transação de advice Mastercard para o Autorizador Presente</t>
   </si>
   <si>
-    <t>aws - Formatador</t>
-  </si>
-  <si>
     <t>Validação e Testes do Autorizador Presente</t>
   </si>
   <si>
     <t>Desativar micro-serviço Fraudes Bandeiras - Gravar transações advice mastercard no mesh</t>
+  </si>
+  <si>
+    <t>Alterar Formatador para direcionar todas as transações para o Autorizador</t>
+  </si>
+  <si>
+    <t>Criar produto(s) para tratar as transações direcionadas pelo Formatador</t>
+  </si>
+  <si>
+    <t>Ver com Regi</t>
+  </si>
+  <si>
+    <t>Necessário aguardar direcionamento do Cores</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>Datadog ?</t>
+  </si>
+  <si>
+    <t>Pavimentação</t>
+  </si>
+  <si>
+    <t>Implementar Cenário 1 - Erro gerado COM ocorrência X0</t>
+  </si>
+  <si>
+    <t>Implementar Cenário 2 - Erro gerado SEM ocorrência X0 - Retorno Segurança</t>
+  </si>
+  <si>
+    <t>mplementar Cenário 2 - Erro gerado SEM ocorrência X0 - Retorno Demais Serviços</t>
+  </si>
+  <si>
+    <t>Implementar Cenário 3 - Erro gerado no próprio Autorizador</t>
+  </si>
+  <si>
+    <t>Implementar Cenário 3 - Erro gerado no Conciliação</t>
+  </si>
+  <si>
+    <t>Motivo de erro Interno (ESTM5)</t>
+  </si>
+  <si>
+    <t>Incluir campo no evento Transação Finalizada e Conciliação Finalizada</t>
+  </si>
+  <si>
+    <t>Alterar Glue Job </t>
+  </si>
+  <si>
+    <t>Incluir Campo na Tabela de Transações</t>
+  </si>
+  <si>
+    <t>Incluir campo no response da API</t>
+  </si>
+  <si>
+    <t>Incluir campo nas tabelas Data Mesh</t>
+  </si>
+  <si>
+    <t>Mapeamento do campo no Autorizadores</t>
+  </si>
+  <si>
+    <t>Realizar mapeamento / engenharia reversa das ocorrências X0 retornadas pelos serviços Contas, Limite operacional e Limite Portador</t>
+  </si>
+  <si>
+    <t>Correlacionar as ocorrências X0  com os códigos de motivo do Autorizador de Crédito</t>
+  </si>
+  <si>
+    <t>Desenvolver De Para: Ocorrência X0 x Motivo Interno mapeando para o novo campo de motivo de erro interno</t>
+  </si>
+  <si>
+    <t>Autorizador</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Mapeamento dos erros retornados pelo Segurança</t>
+  </si>
+  <si>
+    <t>Criar interpretador do retorno do serviço de Segurança para montar o código de erro Interno para o novo campo de motivo de erro interno</t>
+  </si>
+  <si>
+    <t>Implementar Cenário 2 - Erro gerado SEM ocorrência X0 - BC, AQ5, CC</t>
+  </si>
+  <si>
+    <t>Criar interpretador do retorno dos serviços das siglas BC, AQ5 e CC para montar o código de erro Interno para o novo campo de motivo de erro interno</t>
+  </si>
+  <si>
+    <t>Implementar Cenário 2 - Erro gerado SEM ocorrência X0 - Demais Serviços</t>
+  </si>
+  <si>
+    <t>Criar interpretador do retorno dos demais serviços para montar o código de erro Interno para o novo campo de motivo de erro interno</t>
+  </si>
+  <si>
+    <t>Mapeamento dos erros retornados pelos serviços das siglas BC, AQ5 e CC</t>
+  </si>
+  <si>
+    <t>Mapeamento dos erros retornados pelos demais serviços</t>
+  </si>
+  <si>
+    <t>Mapeamento dos erros gerado pelo Autorizador</t>
+  </si>
+  <si>
+    <t>Ajustar Error Handler para tratar o novo campo código motivo erro interno</t>
+  </si>
+  <si>
+    <t>Implementar Cenário 4 - Erro gerado no Conciliação</t>
+  </si>
+  <si>
+    <t>Mapeamento dos erros gerado pelo Conciliação</t>
+  </si>
+  <si>
+    <t>Normalmente é estimado quantidade de horas fixo. 
+Verificar com Marcinha qual a quantidade de horas que normalmente é estimada.</t>
+  </si>
+  <si>
+    <t>Vai depender do andamento do tratamento do decurso de prazo na da sprint 4
+A principio estou estimando 1 sprint</t>
+  </si>
+  <si>
+    <t>Importante aqui um teste no ambiente de produção pra agente analisar como chega no arquivo de chargeback TG52</t>
+  </si>
+  <si>
+    <t>Precisa de uma Oportunidade para definir a solução para que seja possível levantar o esforço.
+A principio estou estimando 3 sprints, sendo 1 para definir solução + refinamento e 2 para iniciar desenvolvimento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deixei na ordem de prioridade (no meu ponto de vista). </t>
+  </si>
+  <si>
+    <t>Mapeamento dos impactos (eventos x consumidores, etc), definição da solução e Refinamento. Poderia ser aberto uma OPR para isso.</t>
+  </si>
+  <si>
+    <t>Pré requisito Camada Zero / Simplificação e Evolução da plataforma.</t>
+  </si>
+  <si>
+    <t>Autorizador Digital</t>
+  </si>
+  <si>
+    <t>ACL Segurança</t>
+  </si>
+  <si>
+    <t>Formatador</t>
+  </si>
+  <si>
+    <t>Autorizador Presente</t>
   </si>
   <si>
     <r>
       <t xml:space="preserve">Pré requisito Camada Zero / Simplificação e Evolução da plataforma
+Estou estimando apenas a MVP 1, conforme detalhamento na aba ESTM3
 </t>
     </r>
     <r>
@@ -312,125 +427,67 @@
     </r>
   </si>
   <si>
-    <t>Alterar Formatador para direcionar todas as transações para o Autorizador</t>
-  </si>
-  <si>
-    <t>Criar produto(s) para tratar as transações direcionadas pelo Formatador</t>
-  </si>
-  <si>
-    <t>aws - Autorizador Presente</t>
-  </si>
-  <si>
-    <t>Ver com Regi</t>
-  </si>
-  <si>
-    <t>Necessário aguardar direcionamento do Cores</t>
-  </si>
-  <si>
-    <t>?</t>
-  </si>
-  <si>
-    <t>Datadog ?</t>
-  </si>
-  <si>
-    <t>Necssário alinhar com o time da Operação / Backoffice que o Chargeback será processado em D+1</t>
-  </si>
-  <si>
-    <t>Pavimentação</t>
-  </si>
-  <si>
-    <t>Implementar Cenário 1 - Erro gerado COM ocorrência X0</t>
-  </si>
-  <si>
-    <t>Implementar Cenário 2 - Erro gerado SEM ocorrência X0 - Retorno Segurança</t>
-  </si>
-  <si>
-    <t>mplementar Cenário 2 - Erro gerado SEM ocorrência X0 - Retorno Demais Serviços</t>
-  </si>
-  <si>
-    <t>Implementar Cenário 3 - Erro gerado no próprio Autorizador</t>
-  </si>
-  <si>
-    <t>Implementar Cenário 3 - Erro gerado no Conciliação</t>
-  </si>
-  <si>
-    <t>Motivo de erro Interno (ESTM5)</t>
-  </si>
-  <si>
-    <t>Incluir campo no evento Transação Finalizada e Conciliação Finalizada</t>
-  </si>
-  <si>
-    <t>Alterar Glue Job </t>
-  </si>
-  <si>
-    <t>Incluir Campo na Tabela de Transações</t>
-  </si>
-  <si>
-    <t>Incluir campo no response da API</t>
-  </si>
-  <si>
-    <t>Incluir campo nas tabelas Data Mesh</t>
-  </si>
-  <si>
-    <t>Mapeamento do campo no Autorizadores</t>
-  </si>
-  <si>
-    <t>Realizar mapeamento / engenharia reversa das ocorrências X0 retornadas pelos serviços Contas, Limite operacional e Limite Portador</t>
-  </si>
-  <si>
-    <t>Correlacionar as ocorrências X0  com os códigos de motivo do Autorizador de Crédito</t>
-  </si>
-  <si>
-    <t>Desenvolver De Para: Ocorrência X0 x Motivo Interno mapeando para o novo campo de motivo de erro interno</t>
-  </si>
-  <si>
-    <t>Autorizador</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Mapeamento dos erros retornados pelo Segurança</t>
-  </si>
-  <si>
-    <t>Criar interpretador do retorno do serviço de Segurança para montar o código de erro Interno para o novo campo de motivo de erro interno</t>
-  </si>
-  <si>
-    <t>Implementar Cenário 2 - Erro gerado SEM ocorrência X0 - BC, AQ5, CC</t>
-  </si>
-  <si>
-    <t>Criar interpretador do retorno dos serviços das siglas BC, AQ5 e CC para montar o código de erro Interno para o novo campo de motivo de erro interno</t>
-  </si>
-  <si>
-    <t>Implementar Cenário 2 - Erro gerado SEM ocorrência X0 - Demais Serviços</t>
-  </si>
-  <si>
-    <t>Criar interpretador do retorno dos demais serviços para montar o código de erro Interno para o novo campo de motivo de erro interno</t>
-  </si>
-  <si>
-    <t>Mapeamento dos erros retornados pelos serviços das siglas BC, AQ5 e CC</t>
-  </si>
-  <si>
-    <t>Mapeamento dos erros retornados pelos demais serviços</t>
-  </si>
-  <si>
-    <t>Mapeamento dos erros gerado pelo Autorizador</t>
-  </si>
-  <si>
-    <t>Ajustar Error Handler para tratar o novo campo código motivo erro interno</t>
-  </si>
-  <si>
-    <t>Implementar Cenário 4 - Erro gerado no Conciliação</t>
-  </si>
-  <si>
-    <t>Mapeamento dos erros gerado pelo Conciliação</t>
+    <t>Gravar 100% das transações no Data Mesh (ESTM4)</t>
+  </si>
+  <si>
+    <t>Gravar 100% das transações no Data Mesh</t>
+  </si>
+  <si>
+    <t>Necssário alinhar com o time da Operação / Backoffice que o Chargeback será processado em D+1
+Essa demanda esta atrelada a modernização da SN xxxxx , cadastrada no Control Tower</t>
+  </si>
+  <si>
+    <t>Conexão direta com o MIP Single Message</t>
+  </si>
+  <si>
+    <t>Contingência / Convivência com o CICS (Mainframe)</t>
+  </si>
+  <si>
+    <t>Conexão da plataforma modernizada com o MIP Single Message</t>
+  </si>
+  <si>
+    <t>Ver com a Alê</t>
+  </si>
+  <si>
+    <t>Criar fila MQ</t>
+  </si>
+  <si>
+    <t>Alterar X0BPAB</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pendente de fechar solução para realizar estimativa
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Será necessário abrir envolvimento para a silga Z2 - CICS</t>
+    </r>
+  </si>
+  <si>
+    <t>Homologação Contábil</t>
+  </si>
+  <si>
+    <t>Homologação de roteiros contábil BG e parametrização Multivisão</t>
+  </si>
+  <si>
+    <t>Motivo de erro Interno</t>
+  </si>
+  <si>
+    <t>Estimativa não fechada</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -473,6 +530,13 @@
       <color rgb="FF000000"/>
       <name val="Helvetica"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1" tint="0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -489,7 +553,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF7030A0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -558,11 +622,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -576,9 +637,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -597,6 +655,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -609,50 +683,33 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -726,13 +783,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>103290</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>151521</xdr:rowOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>170571</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1271,446 +1328,523 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59EE2FA8-ADDF-4863-A88B-6C1D393DF8DA}">
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="56.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="73.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="68.42578125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="73.28515625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+    </row>
+    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5">
+        <v>120</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+    </row>
+    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="5"/>
-    </row>
-    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="6">
-        <v>500</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="6">
-        <v>120</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="5"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <f>ESTM1!C9</f>
         <v>336</v>
       </c>
+      <c r="C7" s="2" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="8" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="6">
+      <c r="A8" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="5">
         <v>360</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+    </row>
+    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="5">
+        <v>40</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="23"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="5">
+        <v>80</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="B15" s="5">
+        <v>120</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="3"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="25"/>
+      <c r="C17" s="26" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="5">
+        <v>120</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="5">
+        <v>80</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="5">
+        <v>160</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="23" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="5"/>
-    </row>
-    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="6">
-        <v>40</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="5"/>
-    </row>
-    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="18">
+      <c r="B21" s="5">
         <v>80</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" s="6">
+      <c r="C21" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="11"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+    </row>
+    <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="5">
         <v>120</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="B16" s="6">
-        <v>80</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B17" s="6">
-        <v>160</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" s="5"/>
-    </row>
-    <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="B20" s="18">
-        <v>120</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B21" s="6">
-        <f>ESTM2!C8</f>
-        <v>344</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B22" s="6">
+      <c r="C24" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="5">
+        <f>ESTM2!C7</f>
+        <v>300</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A26" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="5">
         <f>ESTM3!C6</f>
         <v>120</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" s="19" t="s">
+      <c r="C26" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="3"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" s="28" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="4"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="5"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B28" s="6">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="B32" s="5">
         <f>ESTM4!C5</f>
         <v>200</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B30" s="5"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="B31" s="6">
-        <v>80</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B33" s="5"/>
-    </row>
-    <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="13" t="s">
+      <c r="B35" s="25"/>
+      <c r="C35" s="25"/>
+    </row>
+    <row r="36" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B34" s="6">
+      <c r="B36" s="5">
         <v>120</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="13" t="s">
+      <c r="C36" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C35" s="19" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
+      <c r="B37" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="B38" s="5"/>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>85</v>
-      </c>
+      <c r="B39" s="25"/>
+      <c r="C39" s="25"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="B40" s="18" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
+      <c r="A40" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B42" s="5"/>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="13" t="s">
+      <c r="B43" s="25"/>
+      <c r="C43" s="25"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B43" s="6">
+      <c r="B44" s="5">
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="13" t="s">
+    <row r="45" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A45" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="B44" s="6">
+      <c r="B45" s="5">
         <v>120</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" s="5"/>
+      <c r="C45" s="2" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="13" t="s">
-        <v>18</v>
+      <c r="A47" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="B47" s="25"/>
+      <c r="C47" s="25"/>
+    </row>
+    <row r="48" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="B48" s="24">
+        <f>ESTM6!C5</f>
+        <v>0</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="20" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="B50" s="6">
+      <c r="A49" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C49" s="28" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B51" s="25"/>
+      <c r="C51" s="25"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B52" s="5">
         <f>ESTM5!C3</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="B51" s="6">
+      <c r="C52" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="B53" s="5">
         <f>ESTM5!C11</f>
         <v>166</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="B52" s="6">
+      <c r="C53" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A54" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="B54" s="5">
         <f>ESTM5!C16</f>
         <v>122</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="B53" s="6">
+      <c r="C54" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="B55" s="5">
         <f>ESTM5!C21</f>
         <v>104</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A54" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="B54" s="6">
+      <c r="C55" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A56" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="B56" s="5">
         <f>ESTM5!C26</f>
         <v>104</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="B55" s="6">
+      <c r="C56" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="B57" s="5">
         <f>ESTM5!C31</f>
         <v>128</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="B56" s="6">
+      <c r="C57" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="B58" s="5">
         <f>ESTM5!C36</f>
         <v>128</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="B57" s="6">
+      <c r="C58" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B59" s="5">
         <v>120</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B59" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="C59" s="19" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B62" s="5">
-        <f>SUM(B2:B61)</f>
-        <v>3932</v>
-      </c>
+      <c r="C59" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="C61" s="25" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B64" s="4">
+        <f>SUM(B2:B63)</f>
+        <v>3508</v>
+      </c>
+      <c r="C64" s="29"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1" xr:uid="{59EE2FA8-ADDF-4863-A88B-6C1D393DF8DA}"/>
+  <autoFilter ref="A1:C4" xr:uid="{59EE2FA8-ADDF-4863-A88B-6C1D393DF8DA}"/>
   <hyperlinks>
     <hyperlink ref="A7" location="ESTM1!A1" display="Chargeback (ESTM1)" xr:uid="{A18D599B-3969-435D-86EC-B5E3E10DB233}"/>
-    <hyperlink ref="A21" location="ESTM2!A1" display="Migrar ACL Autenticação no Segurança (ESTM2)" xr:uid="{25C6114A-AFAE-4F85-BD16-E47B9D324FDB}"/>
-    <hyperlink ref="A22" location="ESTM3!A1" display="Desativar micro-serviço Fraudes Bandeiras (ESTM3)" xr:uid="{31331AC1-B46F-4D5F-A6A8-A0BDFCFD76C5}"/>
+    <hyperlink ref="A25" location="ESTM2!A1" display="Migrar ACL Autenticação no Segurança (ESTM2)" xr:uid="{25C6114A-AFAE-4F85-BD16-E47B9D324FDB}"/>
+    <hyperlink ref="A26" location="ESTM3!A1" display="Desativar micro-serviço Fraudes Bandeiras (ESTM3)" xr:uid="{31331AC1-B46F-4D5F-A6A8-A0BDFCFD76C5}"/>
+    <hyperlink ref="A32" location="ESTM4!A1" display="Levar dados para Mesh" xr:uid="{6BC16050-4409-4132-8F73-5FC037415919}"/>
+    <hyperlink ref="A51" location="ESTM5!A1" display="Motivo de erro Interno (ESTM5)" xr:uid="{AEDBA268-D150-4067-A350-70A3FE5AA283}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -1723,104 +1857,104 @@
   <cols>
     <col min="1" max="1" width="55.140625" customWidth="1"/>
     <col min="2" max="2" width="23.140625" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="21"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="B3" s="9"/>
+      <c r="C3" s="10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B5" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="10">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="17"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="12">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="11" t="s">
+      <c r="C7" s="10">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="12">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="12">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="11" t="s">
+      <c r="B8" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="12">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="12">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="12">
+      <c r="C8" s="10">
         <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C9" s="9">
+      <c r="C9" s="7">
         <f>SUM(C3:C8)</f>
         <v>336</v>
       </c>
@@ -1837,100 +1971,91 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F836D3-5F45-41F6-86AB-EE92AD26971D}">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="85.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.140625" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
+      <c r="A1" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="17"/>
+      <c r="A2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="21"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="12">
-        <v>24</v>
+      <c r="A3" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" s="10">
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" s="12">
+      <c r="A4" s="9" t="s">
         <v>60</v>
       </c>
+      <c r="B4" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" s="10">
+        <v>80</v>
+      </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" s="12">
+      <c r="A5" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="10">
         <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="12">
-        <v>90</v>
+      <c r="A6" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="10">
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="12">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C8" s="9">
-        <f>SUM(C3:C7)</f>
-        <v>344</v>
+      <c r="C7" s="7">
+        <f>SUM(C3:C6)</f>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -1949,72 +2074,72 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="89.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
+      <c r="A1" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="17"/>
+      <c r="A2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="21"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="12">
+      <c r="A3" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="10">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" s="12">
+      <c r="A4" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="10">
         <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" s="12">
+      <c r="A5" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="10">
         <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C6" s="9">
+      <c r="C6" s="7">
         <f>SUM(C3:C5)</f>
         <v>120</v>
       </c>
@@ -2035,63 +2160,63 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="69" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
+      <c r="A1" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="17"/>
+      <c r="A2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="21"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="10">
         <v>80</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="12">
-        <v>80</v>
-      </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" s="12">
+      <c r="A4" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="10">
         <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C5" s="9">
+      <c r="C5" s="7">
         <f>SUM(C3:C4)</f>
         <v>200</v>
       </c>
@@ -2111,413 +2236,417 @@
   <dimension ref="A1:O39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="70.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="3"/>
+    <col min="1" max="1" width="70.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="23"/>
+      <c r="A1" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="25"/>
-      <c r="E2" s="23"/>
-      <c r="G2" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="17"/>
+      <c r="A2" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="21"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="28">
+      <c r="A3" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="4">
         <f>SUM(C4:C9)</f>
         <v>120</v>
       </c>
-      <c r="D3" s="25"/>
-      <c r="E3" s="23"/>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30">
+      <c r="A4" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="5">
         <v>16</v>
       </c>
-      <c r="D4" s="25"/>
-      <c r="E4" s="23"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30">
+      <c r="A5" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="5">
         <v>24</v>
       </c>
-      <c r="D5" s="25"/>
-      <c r="E5" s="23"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
-        <v>99</v>
-      </c>
-      <c r="B6" s="30"/>
-      <c r="C6" s="30">
+      <c r="A6" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="5">
         <v>8</v>
       </c>
-      <c r="D6" s="25"/>
-      <c r="E6" s="23"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="B7" s="30"/>
-      <c r="C7" s="30">
+      <c r="A7" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="5">
         <v>24</v>
       </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="23"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
-        <v>97</v>
-      </c>
-      <c r="B8" s="30"/>
-      <c r="C8" s="30">
+      <c r="A8" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="5">
         <v>24</v>
       </c>
-      <c r="D8" s="25"/>
-      <c r="E8" s="23"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="B9" s="30"/>
-      <c r="C9" s="30">
+      <c r="A9" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="5">
         <v>24</v>
       </c>
-      <c r="D9" s="25"/>
-      <c r="E9" s="23"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="25"/>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="23"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="B11" s="31"/>
-      <c r="C11" s="28">
+      <c r="A11" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" s="4">
         <f>SUM(C12:C14)</f>
         <v>166</v>
       </c>
-      <c r="D11" s="25"/>
-      <c r="E11" s="23"/>
     </row>
     <row r="12" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="32" t="s">
-        <v>101</v>
-      </c>
-      <c r="B12" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="31">
+      <c r="A12" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="5">
         <v>60</v>
       </c>
-      <c r="D12" s="25"/>
-      <c r="E12" s="23"/>
     </row>
     <row r="13" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="32" t="s">
-        <v>103</v>
-      </c>
-      <c r="B13" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" s="31">
+      <c r="A13" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="D13" s="25"/>
-      <c r="E13" s="23"/>
+      <c r="B13" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" s="5">
+        <v>90</v>
+      </c>
     </row>
     <row r="14" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="32" t="s">
-        <v>102</v>
-      </c>
-      <c r="B14" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="C14" s="31">
+      <c r="A14" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="5">
         <v>16</v>
       </c>
-      <c r="D14" s="25"/>
-      <c r="E14" s="23"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="25"/>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="23"/>
     </row>
     <row r="16" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="27" t="s">
-        <v>90</v>
-      </c>
-      <c r="B16" s="31"/>
-      <c r="C16" s="28">
+      <c r="A16" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="4">
         <f>SUM(C17:C19)</f>
         <v>122</v>
       </c>
-      <c r="D16" s="25"/>
-      <c r="E16" s="23"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="B17" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="C17" s="31">
+      <c r="A17" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" s="5">
         <v>16</v>
       </c>
-      <c r="D17" s="25"/>
-      <c r="E17" s="23"/>
     </row>
     <row r="18" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="32" t="s">
-        <v>107</v>
-      </c>
-      <c r="B18" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C18" s="31">
+      <c r="A18" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" s="5">
         <v>90</v>
       </c>
-      <c r="D18" s="25"/>
-      <c r="E18" s="23"/>
     </row>
     <row r="19" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="32" t="s">
-        <v>102</v>
-      </c>
-      <c r="B19" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="C19" s="31">
+      <c r="A19" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" s="5">
         <v>16</v>
       </c>
-      <c r="D19" s="25"/>
-      <c r="E19" s="23"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="25"/>
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="23"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="C21" s="5">
+      <c r="A21" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="4">
         <f>SUM(C22:C24)</f>
         <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="B22" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="C22" s="31">
+      <c r="A22" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" s="5">
         <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="32" t="s">
-        <v>109</v>
-      </c>
-      <c r="B23" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C23" s="31">
+      <c r="A23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" s="5">
         <v>80</v>
       </c>
-      <c r="F23" s="33"/>
+      <c r="F23" s="17"/>
     </row>
     <row r="24" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="32" t="s">
-        <v>102</v>
-      </c>
-      <c r="B24" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="C24" s="31">
+      <c r="A24" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" s="5">
         <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="C26" s="5">
+      <c r="A26" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" s="4">
         <f>SUM(C27:C29)</f>
         <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="B27" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="C27" s="31">
+      <c r="A27" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" s="5">
         <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="32" t="s">
-        <v>111</v>
-      </c>
-      <c r="B28" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C28" s="31">
+      <c r="A28" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" s="5">
         <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="32" t="s">
-        <v>102</v>
-      </c>
-      <c r="B29" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="C29" s="31">
+      <c r="A29" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" s="5">
         <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" s="5">
+      <c r="A31" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="4">
         <f>SUM(C32:C34)</f>
         <v>128</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="B32" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="C32" s="31">
+      <c r="A32" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" s="5">
         <v>40</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="32" t="s">
-        <v>115</v>
-      </c>
-      <c r="B33" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C33" s="31">
+      <c r="A33" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C33" s="5">
         <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="32" t="s">
-        <v>102</v>
-      </c>
-      <c r="B34" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="C34" s="31">
+      <c r="A34" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" s="5">
         <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C36" s="5">
+      <c r="A36" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36" s="4">
         <f>SUM(C37:C39)</f>
         <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="B37" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="C37" s="31">
+      <c r="A37" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C37" s="5">
         <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="32" t="s">
-        <v>115</v>
-      </c>
-      <c r="B38" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C38" s="31">
+      <c r="A38" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="5">
         <v>80</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="32" t="s">
-        <v>102</v>
-      </c>
-      <c r="B39" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="C39" s="31">
+      <c r="A39" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C39" s="5">
         <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="G2:O2"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11665A0D-C13A-4F27-8F2D-C3B2EB3999A0}">
+  <dimension ref="A1:O5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="69" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="6" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="21"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="10"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="10"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C5" s="7">
+        <f>SUM(C3:C4)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
